--- a/tame_output/ON/bt/strategyON_20240322.xlsx
+++ b/tame_output/ON/bt/strategyON_20240322.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-383.2%</t>
+          <t>-382.9%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.1%</t>
+          <t>-156.0%</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>-84.9%</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.216062530540225</v>
+        <v>-2.213453869980267</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.20122033391968</v>
+        <v>2.202263798143663</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.390401201530247</v>
+        <v>1.390572453310471</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.922242491367665</v>
+        <v>3.9223452424358</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240322.xlsx
+++ b/tame_output/ON/bt/strategyON_20240322.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-64.9%</t>
+          <t>-66.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>103.9%</t>
+          <t>103.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-58.4%</t>
+          <t>-61.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.3%</t>
+          <t>497.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-382.9%</t>
+          <t>-408.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.0%</t>
+          <t>-166.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,27 +1323,27 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-84.9%</t>
+          <t>-102.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-53.8%</t>
+          <t>-64.6%</t>
         </is>
       </c>
     </row>
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.213453869980267</v>
+        <v>-2.468938447795976</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.202263798143663</v>
+        <v>2.100069967017379</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.390572453310471</v>
+        <v>1.211015189198069</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.9223452424358</v>
+        <v>3.814610883968359</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240322.xlsx
+++ b/tame_output/ON/bt/strategyON_20240322.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>42.0%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-66.3%</t>
+          <t>-65.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>103.3%</t>
+          <t>104.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>119.2%</t>
+          <t>119.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-539.9%</t>
+          <t>-543.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-40.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-61.3%</t>
+          <t>-58.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>497.5%</t>
+          <t>502.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-408.5%</t>
+          <t>-385.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-216.3%</t>
+          <t>-217.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.2%</t>
+          <t>-157.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-280.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.7%</t>
+          <t>-152.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-102.9%</t>
+          <t>-84.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-169.2%</t>
+          <t>-169.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-64.6%</t>
+          <t>-53.5%</t>
         </is>
       </c>
     </row>
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.660425530197474</v>
+        <v>-2.698484962005188</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.075333024814125</v>
+        <v>2.06010925209104</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.003417817992306726</v>
+        <v>0.007083125751400299</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.141910352002246</v>
+        <v>3.144109536657703</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.018075880435823</v>
+        <v>-3.056135312243536</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.928378943375043</v>
+        <v>1.913155170651958</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.3505672244869478</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.923426200515495</v>
+        <v>2.925625385170951</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.02473682065797</v>
+        <v>-3.062796252465684</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.927487493986444</v>
+        <v>1.912263721263359</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.3505672244869478</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.925199127215755</v>
+        <v>2.927398311871211</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.456542613807758</v>
+        <v>-3.494602045615471</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.741098064193933</v>
+        <v>1.725874291470848</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4906500286873084</v>
+        <v>-0.4869847209282148</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.829681516818399</v>
+        <v>2.831880701473855</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.782975142675502</v>
+        <v>-3.821034574483215</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.598809827648927</v>
+        <v>1.583586054925841</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.569452971435363</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.768485341516201</v>
+        <v>2.770684526171657</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.784539293785805</v>
+        <v>-3.822598725593518</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.596764758860771</v>
+        <v>1.581540986137685</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.569452971435363</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.767065933172166</v>
+        <v>2.769265117827622</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.148165538686118</v>
+        <v>-4.186224970493831</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.457801821134887</v>
+        <v>1.442578048411801</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6713399160615824</v>
+        <v>-0.6676746083024888</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.714620511286132</v>
+        <v>2.716819695941588</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.145738474157399</v>
+        <v>-4.183797905965113</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.458027161952206</v>
+        <v>1.44280338922912</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.671672697868734</v>
+        <v>-0.6680073901096404</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.713675357207673</v>
+        <v>2.715874541863128</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.554327251338078</v>
+        <v>-4.592386683145792</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.293353195094693</v>
+        <v>1.278129422371608</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.076596167290319</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.467283634914025</v>
+        <v>2.469482819569481</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.967309735479172</v>
+        <v>-5.005369167286886</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.123345633909716</v>
+        <v>1.108121861186631</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.076596167290319</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.462469067385485</v>
+        <v>2.464668252040942</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.383701609766169</v>
+        <v>-5.421761041573883</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9547829348037946</v>
+        <v>0.9395591620807093</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.076596167290319</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.460463117994363</v>
+        <v>2.462662302649819</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.760378620296014</v>
+        <v>-5.798438052103728</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8143708212605358</v>
+        <v>0.7991470485374506</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.076596167290319</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.470721808663042</v>
+        <v>2.472920993318498</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.774093484621125</v>
+        <v>-5.812152916428839</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.8049844406761864</v>
+        <v>0.7897606679531011</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.076596167290319</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.466821373808737</v>
+        <v>2.469020558464193</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.086918283866105</v>
+        <v>-6.124977715673818</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6782594410331955</v>
+        <v>0.6630356683101102</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.076596167290319</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.465226293863738</v>
+        <v>2.467425478519194</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.091731322331442</v>
+        <v>-6.129790754139155</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.680113201576269</v>
+        <v>0.6648894288531833</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.078142801993105</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.468077288971275</v>
+        <v>2.47027647362673</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.525080430441678</v>
+        <v>-6.563139862249391</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5027472537977715</v>
+        <v>0.4875234810746858</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.078142801993105</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.464050984436871</v>
+        <v>2.466250169092327</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.908081819184309</v>
+        <v>-6.946141250992023</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3494445969791347</v>
+        <v>0.3342208242560494</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.078142801993105</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.463948883115287</v>
+        <v>2.466148067770743</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.283067145355586</v>
+        <v>-7.3211265771633</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.2020219824820542</v>
+        <v>0.1867982097589684</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.453128128164382</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.241529203383951</v>
+        <v>2.243728388039407</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.642597467859588</v>
+        <v>-7.680656899667301</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0635601567785038</v>
+        <v>0.04833638405541807</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.453128128164382</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.246879506682001</v>
+        <v>2.249078691337457</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.968997496524601</v>
+        <v>-8.007056928332315</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05908383473032419</v>
+        <v>-0.07430760745340947</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.783193464588488</v>
+        <v>-1.779528156829395</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.058955509440171</v>
+        <v>2.061154694095627</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.962521349731041</v>
+        <v>-8.000580781538755</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.05345162539113124</v>
+        <v>-0.06867539811421697</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.776717317794929</v>
+        <v>-1.773052010035835</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.065882948138076</v>
+        <v>2.068082132793532</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.95883042477463</v>
+        <v>-7.996889856582343</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.05197525540856685</v>
+        <v>-0.06719902813165213</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.776717317794929</v>
+        <v>-1.773052010035835</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.065882948138076</v>
+        <v>2.068082132793532</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-7.951615071902814</v>
+        <v>-7.989674503710527</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.04357591714119824</v>
+        <v>-0.05879968986428352</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.706939082504547</v>
+        <v>-1.703273774745453</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.113263086430947</v>
+        <v>2.115462271086403</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-7.900587225820987</v>
+        <v>-7.938646657628701</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.01868222422403143</v>
+        <v>-0.03390599694711716</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.631729744197446</v>
+        <v>-1.628064436438352</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.162871243899644</v>
+        <v>2.1650704285551</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-7.827117394153539</v>
+        <v>-7.865176825961253</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.02607740993636876</v>
+        <v>0.01085363721328347</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.558259912529997</v>
+        <v>-1.554594604770904</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.222324844393534</v>
+        <v>2.22452402904899</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.74674503868961</v>
+        <v>-7.784804470497323</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.07278157286945763</v>
+        <v>0.05755780014637235</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.477887557066068</v>
+        <v>-1.474222249306974</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.285103478419408</v>
+        <v>2.287302663074865</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-7.935017841055454</v>
+        <v>-7.973077272863168</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.009746712978476069</v>
+        <v>-0.0249704857015618</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.477887557066068</v>
+        <v>-1.474222249306974</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.277884313517812</v>
+        <v>2.280083498173268</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-7.955182482605001</v>
+        <v>-7.993241914412715</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.0244847603722711</v>
+        <v>-0.03970853309535682</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.498052198615615</v>
+        <v>-1.494386890856522</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.259113337814108</v>
+        <v>2.261312522469564</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.185006929768827</v>
+        <v>-8.22306636157654</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.115298749399245</v>
+        <v>-0.1305225221223307</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.660699735685776</v>
+        <v>-1.657034427926682</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.162640605410568</v>
+        <v>2.164839790066024</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.121937697462487</v>
+        <v>-8.1599971292702</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.08737732784759444</v>
+        <v>-0.1026011005706802</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.68921329836801</v>
+        <v>-1.685547990608916</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.148226196430342</v>
+        <v>2.150425381085798</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.069922183493674</v>
+        <v>-8.107981615301387</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.0625807865736685</v>
+        <v>-0.07780455929675378</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.68921329836801</v>
+        <v>-1.685547990608916</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.152216532116743</v>
+        <v>2.154415716772199</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.151214113047878</v>
+        <v>-8.189273544855592</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.09657278529409208</v>
+        <v>-0.1117965580171774</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.68921329836801</v>
+        <v>-1.685547990608916</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.150741305218001</v>
+        <v>2.152940489873457</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-7.95394470731988</v>
+        <v>-7.992004139127594</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.00261161283802025</v>
+        <v>-0.01783538556110598</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.491943892640012</v>
+        <v>-1.488278584880918</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.284156358819672</v>
+        <v>2.286355543475128</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-7.754792600082781</v>
+        <v>-7.792852031890495</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.0639980964101361</v>
+        <v>0.04877432368705081</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.326621366690198</v>
+        <v>-1.322956058931105</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.370298740742877</v>
+        <v>2.372497925398333</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.52894744736337</v>
+        <v>-7.567006879171084</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.1639152305341094</v>
+        <v>0.1486914578110237</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.284694691103035</v>
+        <v>-1.281029383343941</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.405033819131384</v>
+        <v>2.40723300378684</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.242672635040676</v>
+        <v>-7.280732066848389</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.279564300019246</v>
+        <v>0.2643405272961603</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.284694691103035</v>
+        <v>-1.281029383343941</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.406172963687443</v>
+        <v>2.408372148342899</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.015876807967341</v>
+        <v>-7.053936239775055</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.3729164050106872</v>
+        <v>0.357692632287602</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.21658074648149</v>
+        <v>-1.212915438722397</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.449675104622477</v>
+        <v>2.451874289277933</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.731968077038593</v>
+        <v>-6.770027508846306</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.4922136016208234</v>
+        <v>0.4769898288977377</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.21658074648149</v>
+        <v>-1.212915438722397</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.455408808861114</v>
+        <v>2.45760799351657</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.48498082684564</v>
+        <v>-6.523040258653354</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.5812712393041393</v>
+        <v>0.5660474665810535</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.9695934962885383</v>
+        <v>-0.9659281885294447</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.59386389658302</v>
+        <v>2.596063081238476</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.221143959641571</v>
+        <v>-6.259203391449285</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.6769225048728589</v>
+        <v>0.6616987321497736</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.9695934962885383</v>
+        <v>-0.9659281885294447</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.583980415270112</v>
+        <v>2.586179599925568</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-5.953902158773174</v>
+        <v>-5.991961590580888</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.7819846647208442</v>
+        <v>0.7667608919977589</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.9695934962885383</v>
+        <v>-0.9659281885294447</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.582145854770738</v>
+        <v>2.584345039426195</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.67809299537269</v>
+        <v>-5.716152427180404</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.8920080151075771</v>
+        <v>0.8767842423844914</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.8805741880098048</v>
+        <v>-0.8769088802507112</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.635257124764518</v>
+        <v>2.637456309419974</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.409025407605711</v>
+        <v>-5.447084839413424</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.000303556359862</v>
+        <v>0.9850797836367771</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.6115066002428254</v>
+        <v>-0.6078412924837319</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.797366183570199</v>
+        <v>2.799565368225655</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.144965469282915</v>
+        <v>-5.183024901090628</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.092667215527229</v>
+        <v>1.077443442804143</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.3474466619200293</v>
+        <v>-0.3437813541609357</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.942541830402125</v>
+        <v>2.944741015057581</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.437885845778077</v>
+        <v>-4.47594527758579</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.372712031268863</v>
+        <v>1.357488258545778</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.3474466619200293</v>
+        <v>-0.3437813541609357</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.939754796741824</v>
+        <v>2.94195398139728</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.188244815792125</v>
+        <v>-4.226304247599838</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.472912067151085</v>
+        <v>1.457688294428</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.09780563193407754</v>
+        <v>-0.09414032417498397</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.089883038621236</v>
+        <v>3.092082223276692</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-3.933702916451049</v>
+        <v>-3.971762348258763</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.574095648108272</v>
+        <v>1.558871875385187</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.156736267406998</v>
+        <v>0.1604015751660915</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.241974999446638</v>
+        <v>3.244174184102095</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.700221694221451</v>
+        <v>-3.738281126029164</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.675412565837964</v>
+        <v>1.660188793114879</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.3902174896365965</v>
+        <v>0.3938827973956901</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.38998816162225</v>
+        <v>3.392187346277706</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.520513164077578</v>
+        <v>-3.558572595885292</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.744403767582554</v>
+        <v>1.729179994859469</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.4473889937992926</v>
+        <v>0.4510543015583862</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.421398853806908</v>
+        <v>3.423598038462365</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.388237690446691</v>
+        <v>-3.426297122254405</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.792681443781936</v>
+        <v>1.77745767105885</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.5796644674301793</v>
+        <v>0.5833297751892729</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.496131624732467</v>
+        <v>3.498330809387924</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.197638015773538</v>
+        <v>-3.235697447581252</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.871736374338834</v>
+        <v>1.856512601615748</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.7702641421033322</v>
+        <v>0.7739294498624257</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.613306490223996</v>
+        <v>3.615505674879452</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-2.948638217089958</v>
+        <v>-2.986697648897672</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.984242635035924</v>
+        <v>1.969018862312839</v>
       </c>
       <c r="F1907" t="n">
-        <v>1.019263940786913</v>
+        <v>1.022929248546006</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.775612710657803</v>
+        <v>3.777811895313259</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.757259142229018</v>
+        <v>-2.795318574036731</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.932818335381082</v>
+        <v>1.917594562657996</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.210643015647853</v>
+        <v>1.214308323406946</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.762464225975148</v>
+        <v>3.764663410630604</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.478231846573391</v>
+        <v>-2.516291278381105</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.092973595520419</v>
+        <v>2.077749822797333</v>
       </c>
       <c r="F1909" t="n">
-        <v>1.210643015647853</v>
+        <v>1.214308323406946</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.811008567852235</v>
+        <v>3.813207752507691</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.397886547764345</v>
+        <v>3.700398487700546</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.468938447795976</v>
+        <v>-2.239553103710292</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.100069967017379</v>
+        <v>2.191824104651653</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.211015189198069</v>
+        <v>1.396124984516872</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.814610883968359</v>
+        <v>3.925676761159641</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240322.xlsx
+++ b/tame_output/ON/bt/strategyON_20240322.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-65.2%</t>
+          <t>-63.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>104.2%</t>
+          <t>103.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>119.7%</t>
+          <t>118.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-543.7%</t>
+          <t>-531.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-40.7%</t>
+          <t>-40.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-58.9%</t>
+          <t>-57.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>502.6%</t>
+          <t>491.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-385.5%</t>
+          <t>-372.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-217.9%</t>
+          <t>-212.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-152.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-280.9%</t>
+          <t>-281.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.5%</t>
+          <t>-146.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-84.4%</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-169.0%</t>
+          <t>-169.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-53.5%</t>
+          <t>-125.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1910"/>
+  <dimension ref="A1:G1911"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43635,16 +43635,16 @@
         <v>45292</v>
       </c>
       <c r="B1830" t="n">
-        <v>3.346337136295372</v>
+        <v>3.346337136295373</v>
       </c>
       <c r="C1830" t="n">
         <v>3.127238527942291</v>
       </c>
       <c r="D1830" t="n">
-        <v>1.26606255345954</v>
+        <v>1.35391886434585</v>
       </c>
       <c r="E1830" t="n">
-        <v>3.633307125012359</v>
+        <v>3.668449649366883</v>
       </c>
       <c r="F1830" t="n">
         <v>2.239927473767815</v>
@@ -43664,10 +43664,10 @@
         <v>3.12760327346781</v>
       </c>
       <c r="D1831" t="n">
-        <v>1.24701080845007</v>
+        <v>1.334867119336379</v>
       </c>
       <c r="E1831" t="n">
-        <v>3.62605117253409</v>
+        <v>3.661193696888614</v>
       </c>
       <c r="F1831" t="n">
         <v>2.220875728758345</v>
@@ -43681,16 +43681,16 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085798</v>
+        <v>3.301413393085799</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>1.242410788905723</v>
+        <v>1.330267099792033</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.62667717033905</v>
+        <v>3.661819694693574</v>
       </c>
       <c r="F1832" t="n">
         <v>2.216275709213999</v>
@@ -43704,16 +43704,16 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705544</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>1.194572426659524</v>
+        <v>1.282428737545834</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.604413879342283</v>
+        <v>3.639556403696807</v>
       </c>
       <c r="F1833" t="n">
         <v>2.216275709213999</v>
@@ -43727,16 +43727,16 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.858629459151194</v>
+        <v>0.946485770037504</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.483013301622341</v>
+        <v>3.518155825976864</v>
       </c>
       <c r="F1834" t="n">
         <v>1.880332741705669</v>
@@ -43750,16 +43750,16 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.8580776593093818</v>
+        <v>0.9459339701956918</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.48105041754796</v>
+        <v>3.516192941902484</v>
       </c>
       <c r="F1835" t="n">
         <v>1.881174505190975</v>
@@ -43779,10 +43779,10 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.7523907713670821</v>
+        <v>0.8402470822533921</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.418600934998487</v>
+        <v>3.453743459353011</v>
       </c>
       <c r="F1836" t="n">
         <v>1.866613431488292</v>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.7582401524823265</v>
+        <v>0.8460964633686364</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.421429826170459</v>
+        <v>3.456572350524983</v>
       </c>
       <c r="F1837" t="n">
         <v>1.866613431488292</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.7100178856352429</v>
+        <v>0.7978741965215529</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.406220902053293</v>
+        <v>3.441363426407817</v>
       </c>
       <c r="F1838" t="n">
         <v>1.818391164641208</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4728863937854478</v>
+        <v>0.5607427046717578</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.346309389810916</v>
+        <v>3.38145191416544</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4779239845130344</v>
+        <v>0.5657802953993443</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.346901866287289</v>
+        <v>3.382044390641813</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4214543533367376</v>
+        <v>0.5093106642230475</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.303060395440507</v>
+        <v>3.338202919795031</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3556869632873255</v>
+        <v>0.4435432741736354</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.277771048551212</v>
+        <v>3.312913572905737</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>0.4300077903969258</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.298127411382808</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>0.3482358899691742</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.255501377166946</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>0.2810267820972965</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.233383050851897</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>0.2850182348924867</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.232804428089214</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2009865069470839</v>
+        <v>-0.113130196060774</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.036329422858449</v>
+        <v>3.071471947212972</v>
       </c>
       <c r="F1847" t="n">
         <v>1.450444584979295</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4226084405052014</v>
+        <v>-0.3347521296188914</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.947546866034124</v>
+        <v>2.982689390388647</v>
       </c>
       <c r="F1848" t="n">
         <v>1.412918451291926</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6306124988582786</v>
+        <v>-0.5427561879719687</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.869237387246818</v>
+        <v>2.904379911601342</v>
       </c>
       <c r="F1849" t="n">
         <v>1.412918451291926</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.901012461567164</v>
+        <v>-0.813156150680854</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.756158858501252</v>
+        <v>2.791301382855776</v>
       </c>
       <c r="F1850" t="n">
         <v>1.14251848858304</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.240170839155686</v>
+        <v>-1.152314528269376</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.613579806772292</v>
+        <v>2.648722331126816</v>
       </c>
       <c r="F1851" t="n">
         <v>0.8033601109945183</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.568188060883165</v>
+        <v>-1.480331749996855</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.502711207820068</v>
+        <v>2.537853732174593</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4753428892670392</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.564851314374194</v>
+        <v>-1.476995003487884</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.512144656832226</v>
+        <v>2.54728718118675</v>
       </c>
       <c r="F1853" t="n">
         <v>0.4780349216860705</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.931562366040739</v>
+        <v>-1.843706055154429</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.366566628209339</v>
+        <v>2.401709152563864</v>
       </c>
       <c r="F1854" t="n">
         <v>0.1113238700195249</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.316742756970812</v>
+        <v>-2.228886446084502</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.211037010650174</v>
+        <v>2.246179535004698</v>
       </c>
       <c r="F1855" t="n">
         <v>0.1113238700195249</v>
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.698484962005188</v>
+        <v>-2.572569219311164</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.06010925209104</v>
+        <v>2.110475549168649</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.007083125751400299</v>
+        <v>0.003417817992306726</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.144109536657703</v>
+        <v>3.141910352002246</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.056135312243536</v>
+        <v>-2.930219569549513</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.913155170651958</v>
+        <v>1.963521467729568</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3505672244869478</v>
+        <v>-0.3542325322460414</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.925625385170951</v>
+        <v>2.923426200515495</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.062796252465684</v>
+        <v>-2.93688050977166</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.912263721263359</v>
+        <v>1.962630018340968</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3505672244869478</v>
+        <v>-0.3542325322460414</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.927398311871211</v>
+        <v>2.925199127215755</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.494602045615471</v>
+        <v>-3.368686302921448</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.725874291470848</v>
+        <v>1.776240588548457</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4869847209282148</v>
+        <v>-0.4906500286873084</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.831880701473855</v>
+        <v>2.829681516818399</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.821034574483215</v>
+        <v>-3.695118831789192</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.583586054925841</v>
+        <v>1.633952352003451</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.569452971435363</v>
+        <v>-0.5731182791944566</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.770684526171657</v>
+        <v>2.768485341516201</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.822598725593518</v>
+        <v>-3.696682982899495</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.581540986137685</v>
+        <v>1.631907283215295</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.569452971435363</v>
+        <v>-0.5731182791944566</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.769265117827622</v>
+        <v>2.767065933172166</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.186224970493831</v>
+        <v>-4.060309227799808</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.442578048411801</v>
+        <v>1.492944345489411</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6676746083024888</v>
+        <v>-0.6713399160615824</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.716819695941588</v>
+        <v>2.714620511286132</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.183797905965113</v>
+        <v>-4.057882163271089</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.44280338922912</v>
+        <v>1.49316968630673</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6680073901096404</v>
+        <v>-0.671672697868734</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.715874541863128</v>
+        <v>2.713675357207673</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.592386683145792</v>
+        <v>-4.466470940451767</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.278129422371608</v>
+        <v>1.328495719449218</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.076596167290319</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.469482819569481</v>
+        <v>2.467283634914025</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.005369167286886</v>
+        <v>-4.879453424592861</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.108121861186631</v>
+        <v>1.158488158264241</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.076596167290319</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.464668252040942</v>
+        <v>2.462469067385485</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.421761041573883</v>
+        <v>-5.295845298879859</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9395591620807093</v>
+        <v>0.9899254591583189</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.076596167290319</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.462662302649819</v>
+        <v>2.460463117994363</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.798438052103728</v>
+        <v>-5.672522309409703</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7991470485374506</v>
+        <v>0.8495133456150601</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.076596167290319</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.472920993318498</v>
+        <v>2.470721808663042</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.812152916428839</v>
+        <v>-5.686237173734814</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7897606679531011</v>
+        <v>0.840126965030711</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.076596167290319</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.469020558464193</v>
+        <v>2.466821373808737</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.124977715673818</v>
+        <v>-5.999061972979794</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6630356683101102</v>
+        <v>0.7134019653877202</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.076596167290319</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.467425478519194</v>
+        <v>2.465226293863738</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.129790754139155</v>
+        <v>-6.003875011445131</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6648894288531833</v>
+        <v>0.7152557259307932</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.078142801993105</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.47027647362673</v>
+        <v>2.468077288971275</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.563139862249391</v>
+        <v>-6.437224119555367</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4875234810746858</v>
+        <v>0.5378897781522958</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.078142801993105</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.466250169092327</v>
+        <v>2.464050984436871</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.946141250992023</v>
+        <v>-6.820225508297998</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3342208242560494</v>
+        <v>0.3845871213336594</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.078142801993105</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.466148067770743</v>
+        <v>2.463948883115287</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.3211265771633</v>
+        <v>-7.195210834469275</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1867982097589684</v>
+        <v>0.2371645068365784</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.453128128164382</v>
+        <v>-1.456793435923476</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.243728388039407</v>
+        <v>2.241529203383951</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.680656899667301</v>
+        <v>-7.554741156973277</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.04833638405541807</v>
+        <v>0.09870268113302805</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.453128128164382</v>
+        <v>-1.456793435923476</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.249078691337457</v>
+        <v>2.246879506682001</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.007056928332315</v>
+        <v>-7.88114118563829</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.07430760745340947</v>
+        <v>-0.02394131037579994</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.779528156829395</v>
+        <v>-1.783193464588488</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.061154694095627</v>
+        <v>2.058955509440171</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.000580781538755</v>
+        <v>-7.87466503884473</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.06867539811421697</v>
+        <v>-0.01830910103660699</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.773052010035835</v>
+        <v>-1.776717317794929</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.068082132793532</v>
+        <v>2.065882948138076</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.996889856582343</v>
+        <v>-7.870974113888319</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.06719902813165213</v>
+        <v>-0.01683273105404259</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.773052010035835</v>
+        <v>-1.776717317794929</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.068082132793532</v>
+        <v>2.065882948138076</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-7.989674503710527</v>
+        <v>-7.863758761016503</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.05879968986428352</v>
+        <v>-0.008433392786673544</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.703273774745453</v>
+        <v>-1.706939082504547</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.115462271086403</v>
+        <v>2.113263086430947</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-7.938646657628701</v>
+        <v>-7.812730914934677</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.03390599694711716</v>
+        <v>0.01646030013049282</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.628064436438352</v>
+        <v>-1.631729744197446</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.1650704285551</v>
+        <v>2.162871243899644</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-7.865176825961253</v>
+        <v>-7.739261083267229</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.01085363721328347</v>
+        <v>0.06121993429089301</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.554594604770904</v>
+        <v>-1.558259912529997</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.22452402904899</v>
+        <v>2.222324844393534</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.784804470497323</v>
+        <v>-7.658888727803299</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.05755780014637235</v>
+        <v>0.1079240972239819</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.474222249306974</v>
+        <v>-1.477887557066068</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.287302663074865</v>
+        <v>2.285103478419408</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-7.973077272863168</v>
+        <v>-7.847161530169143</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.0249704857015618</v>
+        <v>0.02539581137604818</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.474222249306974</v>
+        <v>-1.477887557066068</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.280083498173268</v>
+        <v>2.277884313517812</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-7.993241914412715</v>
+        <v>-7.86732617171869</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.03970853309535682</v>
+        <v>0.01065776398225315</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.494386890856522</v>
+        <v>-1.498052198615615</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.261312522469564</v>
+        <v>2.259113337814108</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.22306636157654</v>
+        <v>-8.097150618882516</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.1305225221223307</v>
+        <v>-0.08015622504472075</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.657034427926682</v>
+        <v>-1.660699735685776</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.164839790066024</v>
+        <v>2.162640605410568</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.1599971292702</v>
+        <v>-8.034081386576176</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.1026011005706802</v>
+        <v>-0.05223480349307019</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.685547990608916</v>
+        <v>-1.68921329836801</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.150425381085798</v>
+        <v>2.148226196430342</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.107981615301387</v>
+        <v>-7.982065872607364</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.07780455929675378</v>
+        <v>-0.02743826221914425</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.685547990608916</v>
+        <v>-1.68921329836801</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.154415716772199</v>
+        <v>2.152216532116743</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628916</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.189273544855592</v>
+        <v>-8.063357802161567</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.1117965580171774</v>
+        <v>-0.06143026093956738</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.685547990608916</v>
+        <v>-1.68921329836801</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.152940489873457</v>
+        <v>2.150741305218001</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410713</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-7.992004139127594</v>
+        <v>-7.866088396433569</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.01783538556110598</v>
+        <v>0.032530911516504</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.488278584880918</v>
+        <v>-1.491943892640012</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.286355543475128</v>
+        <v>2.284156358819672</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240573</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-7.792852031890495</v>
+        <v>-7.66693628919647</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.04877432368705081</v>
+        <v>0.09914062076466079</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.322956058931105</v>
+        <v>-1.326621366690198</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.372497925398333</v>
+        <v>2.370298740742877</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085276</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.567006879171084</v>
+        <v>-7.441091136477059</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.1486914578110237</v>
+        <v>0.1990577548886336</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.281029383343941</v>
+        <v>-1.284694691103035</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.40723300378684</v>
+        <v>2.405033819131384</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.280732066848389</v>
+        <v>-7.154816324154365</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.2643405272961603</v>
+        <v>0.3147068243737703</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.281029383343941</v>
+        <v>-1.284694691103035</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.408372148342899</v>
+        <v>2.406172963687443</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.053936239775055</v>
+        <v>-6.928020497081031</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.357692632287602</v>
+        <v>0.4080589293652115</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.212915438722397</v>
+        <v>-1.21658074648149</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.451874289277933</v>
+        <v>2.449675104622477</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.770027508846306</v>
+        <v>-6.644111766152282</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.4769898288977377</v>
+        <v>0.5273561259753476</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.212915438722397</v>
+        <v>-1.21658074648149</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.45760799351657</v>
+        <v>2.455408808861114</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.523040258653354</v>
+        <v>-6.397124515959329</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.5660474665810535</v>
+        <v>0.6164137636586635</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.9659281885294447</v>
+        <v>-0.9695934962885383</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.596063081238476</v>
+        <v>2.59386389658302</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.259203391449285</v>
+        <v>-6.13328764875526</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.6616987321497736</v>
+        <v>0.7120650292273836</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.9659281885294447</v>
+        <v>-0.9695934962885383</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.586179599925568</v>
+        <v>2.583980415270112</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-5.991961590580888</v>
+        <v>-5.866045847886864</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.7667608919977589</v>
+        <v>0.8171271890753684</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.9659281885294447</v>
+        <v>-0.9695934962885383</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.584345039426195</v>
+        <v>2.582145854770738</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.716152427180404</v>
+        <v>-5.59023668448638</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.8767842423844914</v>
+        <v>0.9271505394621014</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.8769088802507112</v>
+        <v>-0.8805741880098048</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.637456309419974</v>
+        <v>2.635257124764518</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.447084839413424</v>
+        <v>-5.3211690967194</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.9850797836367771</v>
+        <v>1.035446080714387</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.6078412924837319</v>
+        <v>-0.6115066002428254</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.799565368225655</v>
+        <v>2.797366183570199</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.183024901090628</v>
+        <v>-5.057109158396604</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.077443442804143</v>
+        <v>1.127809739881753</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.3437813541609357</v>
+        <v>-0.3474466619200293</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.944741015057581</v>
+        <v>2.942541830402125</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.47594527758579</v>
+        <v>-4.350029534891766</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.357488258545778</v>
+        <v>1.407854555623387</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.3437813541609357</v>
+        <v>-0.3474466619200293</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.94195398139728</v>
+        <v>2.939754796741824</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.226304247599838</v>
+        <v>-4.100388504905814</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.457688294428</v>
+        <v>1.50805459150561</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.09414032417498397</v>
+        <v>-0.09780563193407754</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.092082223276692</v>
+        <v>3.089883038621236</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-3.971762348258763</v>
+        <v>-3.845846605564738</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.558871875385187</v>
+        <v>1.609238172462797</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.1604015751660915</v>
+        <v>0.156736267406998</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.244174184102095</v>
+        <v>3.241974999446638</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.738281126029164</v>
+        <v>-3.61236538333514</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.660188793114879</v>
+        <v>1.710555090192488</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.3938827973956901</v>
+        <v>0.3902174896365965</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.392187346277706</v>
+        <v>3.38998816162225</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.558572595885292</v>
+        <v>-3.432656853191267</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.729179994859469</v>
+        <v>1.779546291937078</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.4510543015583862</v>
+        <v>0.4473889937992926</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.423598038462365</v>
+        <v>3.421398853806908</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860424</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.426297122254405</v>
+        <v>-3.30038137956038</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.77745767105885</v>
+        <v>1.82782396813646</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.5833297751892729</v>
+        <v>0.5796644674301793</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.498330809387924</v>
+        <v>3.496131624732467</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575949</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.235697447581252</v>
+        <v>-3.109781704887228</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.856512601615748</v>
+        <v>1.906878898693358</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.7739294498624257</v>
+        <v>0.7702641421033322</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.615505674879452</v>
+        <v>3.613306490223996</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430982</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-2.986697648897672</v>
+        <v>-2.860781906203647</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.969018862312839</v>
+        <v>2.019385159390449</v>
       </c>
       <c r="F1907" t="n">
-        <v>1.022929248546006</v>
+        <v>1.019263940786913</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.777811895313259</v>
+        <v>3.775612710657803</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.795318574036731</v>
+        <v>-2.669402831342707</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.917594562657996</v>
+        <v>1.967960859735606</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.214308323406946</v>
+        <v>1.210643015647853</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.764663410630604</v>
+        <v>3.762464225975148</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.516291278381105</v>
+        <v>-2.39037553568708</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.077749822797333</v>
+        <v>2.128116119874943</v>
       </c>
       <c r="F1909" t="n">
-        <v>1.214308323406946</v>
+        <v>1.210643015647853</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.813207752507691</v>
+        <v>3.811008567852235</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,45 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.700398487700546</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.239553103710292</v>
+        <v>-2.113637361016268</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.191824104651653</v>
+        <v>2.242190401729263</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.396124984516872</v>
+        <v>1.392459676757779</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.925676761159641</v>
+        <v>3.923477576504185</v>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" s="2" t="n">
+        <v>45373</v>
+      </c>
+      <c r="B1911" t="n">
+        <v>3.842275957312457</v>
+      </c>
+      <c r="C1911" t="n">
+        <v>3.216311526909917</v>
+      </c>
+      <c r="D1911" t="n">
+        <v>-2.113637361016268</v>
+      </c>
+      <c r="E1911" t="n">
+        <v>2.242190401729263</v>
+      </c>
+      <c r="F1911" t="n">
+        <v>1.392459676757779</v>
+      </c>
+      <c r="G1911" t="n">
+        <v>3.209375323896285</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240322.xlsx
+++ b/tame_output/ON/bt/strategyON_20240322.xlsx
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.842275957312457</v>
+        <v>3.842275957312456</v>
       </c>
       <c r="C1911" t="n">
         <v>3.216311526909917</v>

--- a/tame_output/ON/bt/strategyON_20240322.xlsx
+++ b/tame_output/ON/bt/strategyON_20240322.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,31 +791,31 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>1.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-63.9%</t>
+          <t>-64.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>103.5%</t>
+          <t>103.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>118.3%</t>
+          <t>119.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-531.1%</t>
+          <t>-539.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-58.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>491.9%</t>
+          <t>500.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-372.9%</t>
+          <t>-381.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-212.8%</t>
+          <t>-216.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.0%</t>
+          <t>-157.9%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-146.3%</t>
+          <t>-146.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-125.1%</t>
+          <t>-133.4%</t>
         </is>
       </c>
     </row>
@@ -43641,10 +43641,10 @@
         <v>3.127238527942291</v>
       </c>
       <c r="D1830" t="n">
-        <v>1.35391886434585</v>
+        <v>1.26606255345954</v>
       </c>
       <c r="E1830" t="n">
-        <v>3.668449649366883</v>
+        <v>3.633307125012359</v>
       </c>
       <c r="F1830" t="n">
         <v>2.239927473767815</v>
@@ -43664,10 +43664,10 @@
         <v>3.12760327346781</v>
       </c>
       <c r="D1831" t="n">
-        <v>1.334867119336379</v>
+        <v>1.24701080845007</v>
       </c>
       <c r="E1831" t="n">
-        <v>3.661193696888614</v>
+        <v>3.62605117253409</v>
       </c>
       <c r="F1831" t="n">
         <v>2.220875728758345</v>
@@ -43687,10 +43687,10 @@
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>1.330267099792033</v>
+        <v>1.242410788905723</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.661819694693574</v>
+        <v>3.62667717033905</v>
       </c>
       <c r="F1832" t="n">
         <v>2.216275709213999</v>
@@ -43710,10 +43710,10 @@
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>1.282428737545834</v>
+        <v>1.194572426659524</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.639556403696807</v>
+        <v>3.604413879342283</v>
       </c>
       <c r="F1833" t="n">
         <v>2.216275709213999</v>
@@ -43733,10 +43733,10 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.946485770037504</v>
+        <v>0.858629459151194</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.518155825976864</v>
+        <v>3.483013301622341</v>
       </c>
       <c r="F1834" t="n">
         <v>1.880332741705669</v>
@@ -43756,10 +43756,10 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.9459339701956918</v>
+        <v>0.8580776593093818</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.516192941902484</v>
+        <v>3.48105041754796</v>
       </c>
       <c r="F1835" t="n">
         <v>1.881174505190975</v>
@@ -43779,10 +43779,10 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.8402470822533921</v>
+        <v>0.7523907713670821</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.453743459353011</v>
+        <v>3.418600934998487</v>
       </c>
       <c r="F1836" t="n">
         <v>1.866613431488292</v>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.8460964633686364</v>
+        <v>0.7582401524823265</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.456572350524983</v>
+        <v>3.421429826170459</v>
       </c>
       <c r="F1837" t="n">
         <v>1.866613431488292</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.7978741965215529</v>
+        <v>0.7100178856352429</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.441363426407817</v>
+        <v>3.406220902053293</v>
       </c>
       <c r="F1838" t="n">
         <v>1.818391164641208</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.5607427046717578</v>
+        <v>0.4728863937854478</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.38145191416544</v>
+        <v>3.346309389810916</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.5657802953993443</v>
+        <v>0.4779239845130344</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.382044390641813</v>
+        <v>3.346901866287289</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.5093106642230475</v>
+        <v>0.4214543533367376</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.338202919795031</v>
+        <v>3.303060395440507</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.4435432741736354</v>
+        <v>0.3556869632873255</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.312913572905737</v>
+        <v>3.277771048551212</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.4300077903969258</v>
+        <v>0.3421514795106159</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.298127411382808</v>
+        <v>3.262984887028284</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.3482358899691742</v>
+        <v>0.2603795790828642</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.255501377166946</v>
+        <v>3.220358852812422</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.2810267820972965</v>
+        <v>0.1931704712109866</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.233383050851897</v>
+        <v>3.198240526497373</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.2850182348924867</v>
+        <v>0.1971619240061768</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.232804428089214</v>
+        <v>3.19766190373469</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.113130196060774</v>
+        <v>-0.2009865069470839</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.071471947212972</v>
+        <v>3.036329422858449</v>
       </c>
       <c r="F1847" t="n">
         <v>1.450444584979295</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.3347521296188914</v>
+        <v>-0.4226084405052014</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.982689390388647</v>
+        <v>2.947546866034124</v>
       </c>
       <c r="F1848" t="n">
         <v>1.412918451291926</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.5427561879719687</v>
+        <v>-0.6306124988582786</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.904379911601342</v>
+        <v>2.869237387246818</v>
       </c>
       <c r="F1849" t="n">
         <v>1.412918451291926</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.813156150680854</v>
+        <v>-0.901012461567164</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.791301382855776</v>
+        <v>2.756158858501252</v>
       </c>
       <c r="F1850" t="n">
         <v>1.14251848858304</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.152314528269376</v>
+        <v>-1.240170839155686</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.648722331126816</v>
+        <v>2.613579806772292</v>
       </c>
       <c r="F1851" t="n">
         <v>0.8033601109945183</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.480331749996855</v>
+        <v>-1.568188060883165</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.537853732174593</v>
+        <v>2.502711207820068</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4753428892670392</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.476995003487884</v>
+        <v>-1.564851314374194</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.54728718118675</v>
+        <v>2.512144656832226</v>
       </c>
       <c r="F1853" t="n">
         <v>0.4780349216860705</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.843706055154429</v>
+        <v>-1.931562366040739</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.401709152563864</v>
+        <v>2.366566628209339</v>
       </c>
       <c r="F1854" t="n">
         <v>0.1113238700195249</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.228886446084502</v>
+        <v>-2.316742756970812</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.246179535004698</v>
+        <v>2.211037010650174</v>
       </c>
       <c r="F1855" t="n">
         <v>0.1113238700195249</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.572569219311164</v>
+        <v>-2.660425530197474</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.110475549168649</v>
+        <v>2.075333024814125</v>
       </c>
       <c r="F1856" t="n">
         <v>0.003417817992306726</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-2.930219569549513</v>
+        <v>-3.018075880435823</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.963521467729568</v>
+        <v>1.928378943375043</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.3542325322460414</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-2.93688050977166</v>
+        <v>-3.02473682065797</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.962630018340968</v>
+        <v>1.927487493986444</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.3542325322460414</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.368686302921448</v>
+        <v>-3.456542613807758</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.776240588548457</v>
+        <v>1.741098064193933</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4906500286873084</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.695118831789192</v>
+        <v>-3.782975142675502</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.633952352003451</v>
+        <v>1.598809827648927</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.5731182791944566</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.696682982899495</v>
+        <v>-3.784539293785805</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.631907283215295</v>
+        <v>1.596764758860771</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.5731182791944566</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.060309227799808</v>
+        <v>-4.148165538686118</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.492944345489411</v>
+        <v>1.457801821134887</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.6713399160615824</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.057882163271089</v>
+        <v>-4.145738474157399</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.49316968630673</v>
+        <v>1.458027161952206</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.671672697868734</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.466470940451767</v>
+        <v>-4.554327251338078</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.328495719449218</v>
+        <v>1.293353195094693</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.080261475049412</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.879453424592861</v>
+        <v>-4.967309735479172</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.158488158264241</v>
+        <v>1.123345633909716</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.080261475049412</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.295845298879859</v>
+        <v>-5.383701609766169</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9899254591583189</v>
+        <v>0.9547829348037946</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.080261475049412</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.672522309409703</v>
+        <v>-5.760378620296014</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8495133456150601</v>
+        <v>0.8143708212605358</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.080261475049412</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.686237173734814</v>
+        <v>-5.774093484621125</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.840126965030711</v>
+        <v>0.8049844406761864</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.080261475049412</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-5.999061972979794</v>
+        <v>-6.086918283866105</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.7134019653877202</v>
+        <v>0.6782594410331955</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.080261475049412</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.003875011445131</v>
+        <v>-6.091731322331442</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.7152557259307932</v>
+        <v>0.680113201576269</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.081808109752198</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.437224119555367</v>
+        <v>-6.525080430441678</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5378897781522958</v>
+        <v>0.5027472537977715</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.081808109752198</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.820225508297998</v>
+        <v>-6.908081819184309</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3845871213336594</v>
+        <v>0.3494445969791347</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.081808109752198</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.195210834469275</v>
+        <v>-7.283067145355586</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.2371645068365784</v>
+        <v>0.2020219824820542</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.456793435923476</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.554741156973277</v>
+        <v>-7.642597467859588</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.09870268113302805</v>
+        <v>0.0635601567785038</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.456793435923476</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.88114118563829</v>
+        <v>-7.968997496524601</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.02394131037579994</v>
+        <v>-0.05908383473032419</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.783193464588488</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.87466503884473</v>
+        <v>-7.962521349731041</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.01830910103660699</v>
+        <v>-0.05345162539113124</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.776717317794929</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.870974113888319</v>
+        <v>-7.95883042477463</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.01683273105404259</v>
+        <v>-0.05197525540856685</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.776717317794929</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-7.863758761016503</v>
+        <v>-7.951615071902814</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.008433392786673544</v>
+        <v>-0.04357591714119824</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.706939082504547</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-7.812730914934677</v>
+        <v>-7.900587225820987</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.01646030013049282</v>
+        <v>-0.01868222422403143</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.631729744197446</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-7.739261083267229</v>
+        <v>-7.827117394153539</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.06121993429089301</v>
+        <v>0.02607740993636876</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.558259912529997</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.658888727803299</v>
+        <v>-7.74674503868961</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.1079240972239819</v>
+        <v>0.07278157286945763</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.477887557066068</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-7.847161530169143</v>
+        <v>-7.935017841055454</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.02539581137604818</v>
+        <v>-0.009746712978476069</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.477887557066068</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-7.86732617171869</v>
+        <v>-7.955182482605001</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.01065776398225315</v>
+        <v>-0.0244847603722711</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.498052198615615</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.097150618882516</v>
+        <v>-8.185006929768827</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.08015622504472075</v>
+        <v>-0.115298749399245</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.660699735685776</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.034081386576176</v>
+        <v>-8.121937697462487</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.05223480349307019</v>
+        <v>-0.08737732784759444</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.68921329836801</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-7.982065872607364</v>
+        <v>-8.069922183493674</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.02743826221914425</v>
+        <v>-0.0625807865736685</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.68921329836801</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.063357802161567</v>
+        <v>-8.151214113047878</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.06143026093956738</v>
+        <v>-0.09657278529409208</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.68921329836801</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-7.866088396433569</v>
+        <v>-7.95394470731988</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.032530911516504</v>
+        <v>-0.00261161283802025</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.491943892640012</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-7.66693628919647</v>
+        <v>-7.754792600082781</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.09914062076466079</v>
+        <v>0.0639980964101361</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.326621366690198</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.441091136477059</v>
+        <v>-7.52894744736337</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.1990577548886336</v>
+        <v>0.1639152305341094</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.284694691103035</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.154816324154365</v>
+        <v>-7.242672635040676</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.3147068243737703</v>
+        <v>0.279564300019246</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.284694691103035</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-6.928020497081031</v>
+        <v>-7.015876807967341</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.4080589293652115</v>
+        <v>0.3729164050106872</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.21658074648149</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.644111766152282</v>
+        <v>-6.731968077038593</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.5273561259753476</v>
+        <v>0.4922136016208234</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.21658074648149</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.397124515959329</v>
+        <v>-6.48498082684564</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.6164137636586635</v>
+        <v>0.5812712393041393</v>
       </c>
       <c r="F1894" t="n">
         <v>-0.9695934962885383</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.13328764875526</v>
+        <v>-6.221143959641571</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.7120650292273836</v>
+        <v>0.6769225048728589</v>
       </c>
       <c r="F1895" t="n">
         <v>-0.9695934962885383</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-5.866045847886864</v>
+        <v>-5.953902158773174</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.8171271890753684</v>
+        <v>0.7819846647208442</v>
       </c>
       <c r="F1896" t="n">
         <v>-0.9695934962885383</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.59023668448638</v>
+        <v>-5.67809299537269</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.9271505394621014</v>
+        <v>0.8920080151075771</v>
       </c>
       <c r="F1897" t="n">
         <v>-0.8805741880098048</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.3211690967194</v>
+        <v>-5.409025407605711</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.035446080714387</v>
+        <v>1.000303556359862</v>
       </c>
       <c r="F1898" t="n">
         <v>-0.6115066002428254</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.057109158396604</v>
+        <v>-5.144965469282915</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.127809739881753</v>
+        <v>1.092667215527229</v>
       </c>
       <c r="F1899" t="n">
         <v>-0.3474466619200293</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.350029534891766</v>
+        <v>-4.437885845778077</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.407854555623387</v>
+        <v>1.372712031268863</v>
       </c>
       <c r="F1900" t="n">
         <v>-0.3474466619200293</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.100388504905814</v>
+        <v>-4.188244815792125</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.50805459150561</v>
+        <v>1.472912067151085</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.09780563193407754</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-3.845846605564738</v>
+        <v>-3.933702916451049</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.609238172462797</v>
+        <v>1.574095648108272</v>
       </c>
       <c r="F1902" t="n">
         <v>0.156736267406998</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.61236538333514</v>
+        <v>-3.700221694221451</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.710555090192488</v>
+        <v>1.675412565837964</v>
       </c>
       <c r="F1903" t="n">
         <v>0.3902174896365965</v>
@@ -45340,19 +45340,19 @@
         <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.152965457527332</v>
+        <v>3.129043666404221</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.432656853191267</v>
+        <v>-3.520513164077578</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.779546291937078</v>
+        <v>1.720481976459443</v>
       </c>
       <c r="F1904" t="n">
         <v>0.4473889937992926</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.421398853806908</v>
+        <v>3.397477062683797</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.124411153151248</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.30038137956038</v>
+        <v>-3.388237690446691</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.82782396813646</v>
+        <v>1.768759652658825</v>
       </c>
       <c r="F1905" t="n">
         <v>0.5796644674301793</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.496131624732467</v>
+        <v>3.472209833609356</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.127226213838885</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.109781704887228</v>
+        <v>-3.197638015773538</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.906878898693358</v>
+        <v>1.847814583215722</v>
       </c>
       <c r="F1906" t="n">
         <v>0.7702641421033322</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.613306490223996</v>
+        <v>3.589384699100885</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.140132555062544</v>
       </c>
       <c r="D1907" t="n">
-        <v>-2.860781906203647</v>
+        <v>-2.948638217089958</v>
       </c>
       <c r="E1907" t="n">
-        <v>2.019385159390449</v>
+        <v>1.960320843912814</v>
       </c>
       <c r="F1907" t="n">
         <v>1.019263940786913</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.775612710657803</v>
+        <v>3.751690919534692</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>3.012156625463325</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.669402831342707</v>
+        <v>-2.757259142229018</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.967960859735606</v>
+        <v>1.90889654425797</v>
       </c>
       <c r="F1908" t="n">
         <v>1.210643015647853</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.762464225975148</v>
+        <v>3.738542434852037</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>3.060700967340411</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.39037553568708</v>
+        <v>-2.478231846573391</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.128116119874943</v>
+        <v>2.069051804397307</v>
       </c>
       <c r="F1909" t="n">
         <v>1.210643015647853</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.811008567852235</v>
+        <v>3.787086776729123</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.088001770449517</v>
+        <v>3.064079979326406</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.113637361016268</v>
+        <v>-2.201493671902579</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.242190401729263</v>
+        <v>2.183126086251627</v>
       </c>
       <c r="F1910" t="n">
         <v>1.392459676757779</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.923477576504185</v>
+        <v>3.899555785381073</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.842275957312456</v>
+        <v>3.795597916835048</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.216311526909917</v>
+        <v>3.133383364849424</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.113637361016268</v>
+        <v>-2.201493671902579</v>
       </c>
       <c r="E1911" t="n">
-        <v>2.242190401729263</v>
+        <v>2.183126086251627</v>
       </c>
       <c r="F1911" t="n">
         <v>1.392459676757779</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.209375323896285</v>
+        <v>3.126447161835792</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240322.xlsx
+++ b/tame_output/ON/bt/strategyON_20240322.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>-20.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-64.8%</t>
+          <t>-65.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>103.9%</t>
+          <t>103.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-58.5%</t>
+          <t>-60.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>500.5%</t>
+          <t>499.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-381.7%</t>
+          <t>-400.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.9%</t>
+          <t>-165.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-146.4%</t>
+          <t>-152.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-94.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-133.4%</t>
+          <t>-155.3%</t>
         </is>
       </c>
     </row>
@@ -45343,16 +45343,16 @@
         <v>3.129043666404221</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.520513164077578</v>
+        <v>-3.692455450553654</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.720481976459443</v>
+        <v>1.651705061869012</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.4473889937992926</v>
+        <v>0.3764664133832471</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.397477062683797</v>
+        <v>3.35492351443417</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.124411153151248</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.388237690446691</v>
+        <v>-3.560179976922767</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.768759652658825</v>
+        <v>1.699982738068394</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.5796644674301793</v>
+        <v>0.5087418870141338</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.472209833609356</v>
+        <v>3.429656285359729</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.127226213838885</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.197638015773538</v>
+        <v>-3.369580302249615</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.847814583215722</v>
+        <v>1.779037668625292</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.7702641421033322</v>
+        <v>0.6993415616872867</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.589384699100885</v>
+        <v>3.546831150851257</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.140132555062544</v>
       </c>
       <c r="D1907" t="n">
-        <v>-2.948638217089958</v>
+        <v>-3.120580503566034</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.960320843912814</v>
+        <v>1.891543929322383</v>
       </c>
       <c r="F1907" t="n">
-        <v>1.019263940786913</v>
+        <v>0.9483413603708674</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.751690919534692</v>
+        <v>3.709137371285065</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.012156625463325</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.757259142229018</v>
+        <v>-2.929201428705094</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.90889654425797</v>
+        <v>1.84011962966754</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.210643015647853</v>
+        <v>1.139720435231808</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.738542434852037</v>
+        <v>3.69598888660241</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.060700967340411</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.478231846573391</v>
+        <v>-2.650174133049467</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.069051804397307</v>
+        <v>2.000274889806877</v>
       </c>
       <c r="F1909" t="n">
-        <v>1.210643015647853</v>
+        <v>1.139720435231808</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.787086776729123</v>
+        <v>3.744533228479496</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.064079979326406</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.201493671902579</v>
+        <v>-2.388699129815281</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.183126086251627</v>
+        <v>2.108243903086546</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.392459676757779</v>
+        <v>1.295199990897013</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.899555785381073</v>
+        <v>3.841199973864613</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.795597916835048</v>
+        <v>3.543007929779489</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.133383364849424</v>
+        <v>2.913908600243821</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.201493671902579</v>
+        <v>-2.388699129815281</v>
       </c>
       <c r="E1911" t="n">
-        <v>2.183126086251627</v>
+        <v>2.108243903086546</v>
       </c>
       <c r="F1911" t="n">
-        <v>1.392459676757779</v>
+        <v>1.295199990897013</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.126447161835792</v>
+        <v>2.906972397230189</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240322.xlsx
+++ b/tame_output/ON/bt/strategyON_20240322.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-17.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-65.9%</t>
+          <t>-66.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>103.6%</t>
+          <t>104.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>119.2%</t>
+          <t>119.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-41.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.8%</t>
+          <t>498.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-400.4%</t>
+          <t>-401.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-165.4%</t>
+          <t>-178.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.7%</t>
+          <t>-150.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-94.5%</t>
+          <t>-96.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-155.3%</t>
+          <t>-75.5%</t>
         </is>
       </c>
     </row>
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-7.951615071902814</v>
+        <v>-8.110463100664264</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.04357591714119824</v>
+        <v>-0.1071151286457779</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.706939082504547</v>
+        <v>-1.880021388022765</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.113263086430947</v>
+        <v>2.009413703120016</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-7.900587225820987</v>
+        <v>-8.059435254582437</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.01868222422403143</v>
+        <v>-0.08222143572861151</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.631729744197446</v>
+        <v>-1.804812049715664</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.162871243899644</v>
+        <v>2.059021860588713</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-7.827117394153539</v>
+        <v>-7.985965422914989</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.02607740993636876</v>
+        <v>-0.03746180156821133</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.558259912529997</v>
+        <v>-1.731342218048216</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.222324844393534</v>
+        <v>2.118475461082603</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.74674503868961</v>
+        <v>-7.905593067451059</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.07278157286945763</v>
+        <v>0.009242361364877549</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.477887557066068</v>
+        <v>-1.650969862584286</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.285103478419408</v>
+        <v>2.181254095108478</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-7.935017841055454</v>
+        <v>-8.093865869816904</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.009746712978476069</v>
+        <v>-0.07328592448305615</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.477887557066068</v>
+        <v>-1.650969862584286</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.277884313517812</v>
+        <v>2.174034930206882</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-7.955182482605001</v>
+        <v>-8.114030511366451</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.0244847603722711</v>
+        <v>-0.08802397187685118</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.498052198615615</v>
+        <v>-1.671134504133833</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.259113337814108</v>
+        <v>2.155263954503177</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.185006929768827</v>
+        <v>-8.343854958530276</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.115298749399245</v>
+        <v>-0.1788379609038246</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.660699735685776</v>
+        <v>-1.833782041203994</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.162640605410568</v>
+        <v>2.058791222099637</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.121937697462487</v>
+        <v>-8.280785726223936</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.08737732784759444</v>
+        <v>-0.1509165393521741</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.68921329836801</v>
+        <v>-1.862295603886228</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.148226196430342</v>
+        <v>2.044376813119411</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.069922183493674</v>
+        <v>-8.228770212255123</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.0625807865736685</v>
+        <v>-0.1261199980782481</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.68921329836801</v>
+        <v>-1.862295603886228</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.152216532116743</v>
+        <v>2.048367148805812</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.151214113047878</v>
+        <v>-8.310062141809327</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.09657278529409208</v>
+        <v>-0.1601119967986717</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.68921329836801</v>
+        <v>-1.862295603886228</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.150741305218001</v>
+        <v>2.04689192190707</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-7.95394470731988</v>
+        <v>-8.11279273608133</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.00261161283802025</v>
+        <v>-0.06615082434260033</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.491943892640012</v>
+        <v>-1.66502619815823</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.284156358819672</v>
+        <v>2.180306975508741</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-7.754792600082781</v>
+        <v>-7.913640628844231</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.0639980964101361</v>
+        <v>0.0004588849055564559</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.326621366690198</v>
+        <v>-1.499703672208417</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.370298740742877</v>
+        <v>2.266449357431946</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.52894744736337</v>
+        <v>-7.68779547612482</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.1639152305341094</v>
+        <v>0.1003760190295293</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.284694691103035</v>
+        <v>-1.457776996621253</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.405033819131384</v>
+        <v>2.301184435820453</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.242672635040676</v>
+        <v>-7.401520663802126</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.279564300019246</v>
+        <v>0.216025088514666</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.284694691103035</v>
+        <v>-1.457776996621253</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.406172963687443</v>
+        <v>2.302323580376512</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.015876807967341</v>
+        <v>-7.174724836728792</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.3729164050106872</v>
+        <v>0.3093771935061067</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.21658074648149</v>
+        <v>-1.389663051999709</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.449675104622477</v>
+        <v>2.345825721311546</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.731968077038593</v>
+        <v>-6.890816105800043</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.4922136016208234</v>
+        <v>0.4286743901162429</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.21658074648149</v>
+        <v>-1.389663051999709</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.455408808861114</v>
+        <v>2.351559425550183</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.48498082684564</v>
+        <v>-6.643828855607091</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.5812712393041393</v>
+        <v>0.5177320277995587</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.9695934962885383</v>
+        <v>-1.142675801806757</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.59386389658302</v>
+        <v>2.490014513272089</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.221143959641571</v>
+        <v>-6.379991988403022</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.6769225048728589</v>
+        <v>0.6133832933682788</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.9695934962885383</v>
+        <v>-1.142675801806757</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.583980415270112</v>
+        <v>2.480131031959181</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-5.953902158773174</v>
+        <v>-6.112750187534625</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.7819846647208442</v>
+        <v>0.7184454532162636</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.9695934962885383</v>
+        <v>-1.142675801806757</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.582145854770738</v>
+        <v>2.478296471459807</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.67809299537269</v>
+        <v>-5.836941024134141</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.8920080151075771</v>
+        <v>0.8284688036029966</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.8805741880098048</v>
+        <v>-1.053656493528023</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.635257124764518</v>
+        <v>2.531407741453587</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.409025407605711</v>
+        <v>-5.567873436367162</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.000303556359862</v>
+        <v>0.9367643448552823</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.6115066002428254</v>
+        <v>-0.7845889057610437</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.797366183570199</v>
+        <v>2.693516800259268</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.144965469282915</v>
+        <v>-5.303813498044366</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.092667215527229</v>
+        <v>1.029128004022648</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.3474466619200293</v>
+        <v>-0.5205289674382475</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.942541830402125</v>
+        <v>2.838692447091193</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.437885845778077</v>
+        <v>-4.596733874539527</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.372712031268863</v>
+        <v>1.309172819764283</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.3474466619200293</v>
+        <v>-0.5205289674382475</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.939754796741824</v>
+        <v>2.835905413430893</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.188244815792125</v>
+        <v>-4.347092844553575</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.472912067151085</v>
+        <v>1.409372855646505</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.09780563193407754</v>
+        <v>-0.2708879374522958</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.089883038621236</v>
+        <v>2.986033655310305</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-3.933702916451049</v>
+        <v>-4.0925509452125</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.574095648108272</v>
+        <v>1.510556436603692</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.156736267406998</v>
+        <v>-0.01634603811122026</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.241974999446638</v>
+        <v>3.138125616135707</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.700221694221451</v>
+        <v>-3.859069722982901</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.675412565837964</v>
+        <v>1.611873354333384</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.3902174896365965</v>
+        <v>0.2171351841183783</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.38998816162225</v>
+        <v>3.286138778311319</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.129043666404221</v>
+        <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.692455450553654</v>
+        <v>-3.848468374737023</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.651705061869012</v>
+        <v>1.613221683318776</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.3764664133832471</v>
+        <v>0.2041575274987915</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.35492351443417</v>
+        <v>3.275459974026607</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.124411153151248</v>
+        <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.560179976922767</v>
+        <v>-3.716192901106137</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.699982738068394</v>
+        <v>1.661499359518158</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.5087418870141338</v>
+        <v>0.3364330011296782</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.429656285359729</v>
+        <v>3.350192744952166</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.127226213838885</v>
+        <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.369580302249615</v>
+        <v>-3.525593226432984</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.779037668625292</v>
+        <v>1.740554290075055</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.6993415616872867</v>
+        <v>0.527032675802831</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.546831150851257</v>
+        <v>3.467367610443695</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.140132555062544</v>
+        <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.120580503566034</v>
+        <v>-3.276593427749404</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.891543929322383</v>
+        <v>1.853060550772146</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.9483413603708674</v>
+        <v>0.7760324744864117</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.709137371285065</v>
+        <v>3.629673830877502</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.012156625463325</v>
+        <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.929201428705094</v>
+        <v>-3.085214352888463</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.84011962966754</v>
+        <v>1.801636251117304</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.139720435231808</v>
+        <v>0.9674115493473517</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.69598888660241</v>
+        <v>3.616525346194848</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.060700967340411</v>
+        <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.650174133049467</v>
+        <v>-2.806187057232837</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.000274889806877</v>
+        <v>1.96179151125664</v>
       </c>
       <c r="F1909" t="n">
-        <v>1.139720435231808</v>
+        <v>0.9674115493473517</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.744533228479496</v>
+        <v>3.665069688071934</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.064079979326406</v>
+        <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.388699129815281</v>
+        <v>-2.529448882562024</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.108243903086546</v>
+        <v>2.07586579311096</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.295199990897013</v>
+        <v>1.149228210457278</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.841199973864613</v>
+        <v>3.777538696723884</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.543007929779489</v>
+        <v>3.441529784000618</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.913908600243821</v>
+        <v>2.937830391366933</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.388699129815281</v>
+        <v>-2.399500911301292</v>
       </c>
       <c r="E1911" t="n">
-        <v>2.108243903086546</v>
+        <v>1.977673602532668</v>
       </c>
       <c r="F1911" t="n">
-        <v>1.295199990897013</v>
+        <v>1.279176181718009</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.906972397230189</v>
+        <v>3.705336100397738</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240322.xlsx
+++ b/tame_output/ON/bt/strategyON_20240322.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-3.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-66.1%</t>
+          <t>-65.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>104.0%</t>
+          <t>104.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>119.5%</t>
+          <t>119.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-41.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-60.3%</t>
+          <t>-59.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.6%</t>
+          <t>499.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-401.5%</t>
+          <t>-390.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-178.5%</t>
+          <t>-159.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-150.6%</t>
+          <t>-150.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-96.1%</t>
+          <t>-91.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-58.7%</t>
         </is>
       </c>
     </row>
@@ -43635,7 +43635,7 @@
         <v>45292</v>
       </c>
       <c r="B1830" t="n">
-        <v>3.346337136295373</v>
+        <v>3.346337136295372</v>
       </c>
       <c r="C1830" t="n">
         <v>3.127238527942291</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082125</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.110463100664264</v>
+        <v>-8.163088600104492</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1071151286457779</v>
+        <v>-0.1281653284218693</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.880021388022765</v>
+        <v>-1.904356262408918</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.009413703120016</v>
+        <v>1.994812778488325</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.059435254582437</v>
+        <v>-8.112060754022666</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.08222143572861151</v>
+        <v>-0.103271635504703</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.804812049715664</v>
+        <v>-1.829146924101817</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.059021860588713</v>
+        <v>2.044420935957021</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-7.985965422914989</v>
+        <v>-8.038590922355217</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.03746180156821133</v>
+        <v>-0.05851200134430234</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.731342218048216</v>
+        <v>-1.755677092434368</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.118475461082603</v>
+        <v>2.103874536450911</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.905593067451059</v>
+        <v>-7.958218566891287</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.009242361364877549</v>
+        <v>-0.01180783841121347</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.650969862584286</v>
+        <v>-1.675304736970439</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.181254095108478</v>
+        <v>2.166653170476786</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.093865869816904</v>
+        <v>-8.146491369257131</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.07328592448305615</v>
+        <v>-0.09433612425914673</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.650969862584286</v>
+        <v>-1.675304736970439</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.174034930206882</v>
+        <v>2.15943400557519</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.114030511366451</v>
+        <v>-8.166656010806678</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.08802397187685118</v>
+        <v>-0.1090741716529418</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.671134504133833</v>
+        <v>-1.695469378519986</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.155263954503177</v>
+        <v>2.140663029871485</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.343854958530276</v>
+        <v>-8.396480457970503</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.1788379609038246</v>
+        <v>-0.1998881606799157</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.833782041203994</v>
+        <v>-1.858116915590146</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.058791222099637</v>
+        <v>2.044190297467946</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.280785726223936</v>
+        <v>-8.333411225664163</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.1509165393521741</v>
+        <v>-0.1719667391282651</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.862295603886228</v>
+        <v>-1.886630478272381</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.044376813119411</v>
+        <v>2.02977588848772</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.228770212255123</v>
+        <v>-8.28139571169535</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.1261199980782481</v>
+        <v>-0.1471701978543387</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.862295603886228</v>
+        <v>-1.886630478272381</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.048367148805812</v>
+        <v>2.03376622417412</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.310062141809327</v>
+        <v>-8.362687641249554</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.1601119967986717</v>
+        <v>-0.1811621965747623</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.862295603886228</v>
+        <v>-1.886630478272381</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.04689192190707</v>
+        <v>2.032290997275378</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.11279273608133</v>
+        <v>-8.165418235521557</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.06615082434260033</v>
+        <v>-0.08720102411869091</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.66502619815823</v>
+        <v>-1.689361072544382</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.180306975508741</v>
+        <v>2.16570605087705</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-7.913640628844231</v>
+        <v>-7.966266128284458</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.0004588849055564559</v>
+        <v>-0.02059131487053456</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.499703672208417</v>
+        <v>-1.524038546594569</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.266449357431946</v>
+        <v>2.251848432800255</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.68779547612482</v>
+        <v>-7.740420975565047</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.1003760190295293</v>
+        <v>0.07932581925343873</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.457776996621253</v>
+        <v>-1.482111871007405</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.301184435820453</v>
+        <v>2.286583511188762</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.401520663802126</v>
+        <v>-7.454146163242353</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.216025088514666</v>
+        <v>0.1949748887385749</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.457776996621253</v>
+        <v>-1.482111871007405</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.302323580376512</v>
+        <v>2.287722655744821</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.174724836728792</v>
+        <v>-7.227350336169019</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.3093771935061067</v>
+        <v>0.2883269937300161</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.389663051999709</v>
+        <v>-1.413997926385861</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.345825721311546</v>
+        <v>2.331224796679855</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.890816105800043</v>
+        <v>-6.94344160524027</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.4286743901162429</v>
+        <v>0.4076241903401523</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.389663051999709</v>
+        <v>-1.413997926385861</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.351559425550183</v>
+        <v>2.336958500918491</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.643828855607091</v>
+        <v>-6.696454355047318</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.5177320277995587</v>
+        <v>0.4966818280234682</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.142675801806757</v>
+        <v>-1.167010676192909</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.490014513272089</v>
+        <v>2.475413588640397</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.379991988403022</v>
+        <v>-6.432617487843249</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.6133832933682788</v>
+        <v>0.5923330935921878</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.142675801806757</v>
+        <v>-1.167010676192909</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.480131031959181</v>
+        <v>2.46553010732749</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.112750187534625</v>
+        <v>-6.165375686974852</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.7184454532162636</v>
+        <v>0.6973952534401731</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.142675801806757</v>
+        <v>-1.167010676192909</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.478296471459807</v>
+        <v>2.463695546828116</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.836941024134141</v>
+        <v>-5.889566523574368</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.8284688036029966</v>
+        <v>0.807418603826906</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.053656493528023</v>
+        <v>-1.077991367914175</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.531407741453587</v>
+        <v>2.516806816821895</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.567873436367162</v>
+        <v>-5.620498935807388</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.9367643448552823</v>
+        <v>0.9157141450791912</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.7845889057610437</v>
+        <v>-0.8089237801471961</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.693516800259268</v>
+        <v>2.678915875627577</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.303813498044366</v>
+        <v>-5.356438997484593</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.029128004022648</v>
+        <v>1.008077804246557</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.5205289674382475</v>
+        <v>-0.5448638418244</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.838692447091193</v>
+        <v>2.824091522459502</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309725</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.596733874539527</v>
+        <v>-4.649359373979754</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.309172819764283</v>
+        <v>1.288122619988192</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.5205289674382475</v>
+        <v>-0.5448638418244</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.835905413430893</v>
+        <v>2.821304488799201</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.347092844553575</v>
+        <v>-4.399718343993802</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.409372855646505</v>
+        <v>1.388322655870414</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.2708879374522958</v>
+        <v>-0.2952228118384482</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.986033655310305</v>
+        <v>2.971432730678614</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.0925509452125</v>
+        <v>-4.145176444652726</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.510556436603692</v>
+        <v>1.489506236827602</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.01634603811122026</v>
+        <v>-0.04068091249737271</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.138125616135707</v>
+        <v>3.123524691504016</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.859069722982901</v>
+        <v>-3.911695222423128</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.611873354333384</v>
+        <v>1.590823154557293</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.2171351841183783</v>
+        <v>0.1928003097322258</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.286138778311319</v>
+        <v>3.271537853679627</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.848468374737023</v>
+        <v>-3.731986692279255</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.613221683318776</v>
+        <v>1.659814356301883</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.2041575274987915</v>
+        <v>0.249971813894922</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.275459974026607</v>
+        <v>3.302948545864286</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.716192901106137</v>
+        <v>-3.599711218648369</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.661499359518158</v>
+        <v>1.708092032501265</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.3364330011296782</v>
+        <v>0.3822472875258086</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.350192744952166</v>
+        <v>3.377681316789845</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.525593226432984</v>
+        <v>-3.409111543975216</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.740554290075055</v>
+        <v>1.787146963058162</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.527032675802831</v>
+        <v>0.5728469621989615</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.467367610443695</v>
+        <v>3.494856182281374</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.276593427749404</v>
+        <v>-3.160111745291636</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.853060550772146</v>
+        <v>1.899653223755253</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.7760324744864117</v>
+        <v>0.8218467608825422</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.629673830877502</v>
+        <v>3.65716240271518</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.085214352888463</v>
+        <v>-2.968732670430696</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.801636251117304</v>
+        <v>1.848228924100411</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.9674115493473517</v>
+        <v>1.013225835743482</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.616525346194848</v>
+        <v>3.644013918032526</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.806187057232837</v>
+        <v>-2.689705374775069</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.96179151125664</v>
+        <v>2.008384184239748</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.9674115493473517</v>
+        <v>1.013225835743482</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.665069688071934</v>
+        <v>3.692558259909612</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.529448882562024</v>
+        <v>-2.412967200104256</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.07586579311096</v>
+        <v>2.122458466094067</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.149228210457278</v>
+        <v>1.195042496853408</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.777538696723884</v>
+        <v>3.805027268561562</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.441529784000618</v>
+        <v>3.44152978400062</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.937830391366933</v>
+        <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.399500911301292</v>
+        <v>-2.284744962182363</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.977673602532668</v>
+        <v>2.165033375009346</v>
       </c>
       <c r="F1911" t="n">
-        <v>1.279176181718009</v>
+        <v>1.323264734775302</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.705336100397738</v>
+        <v>3.873246625061221</v>
       </c>
     </row>
   </sheetData>
